--- a/docs/03_detail_design/単体テスト仕様書.xlsx
+++ b/docs/03_detail_design/単体テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0EE838-A174-48F5-AD43-769C5170B62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3D8B95-27D8-4BDA-A4C6-946711E79A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-16335" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="182">
   <si>
     <t>勤怠管理アプリ
 単体テスト仕様書</t>
@@ -64,6 +64,9 @@
     <t>版数</t>
   </si>
   <si>
+    <t>1.0</t>
+  </si>
+  <si>
     <t>勤怠管理アプリの画面単位テスト観点（詳細設計フェーズ）※一部JUnitによるロジック確認を含む</t>
   </si>
   <si>
@@ -151,7 +154,7 @@
     <t>有効なログインIDと誤ったパスワードを入力する。</t>
   </si>
   <si>
-    <t>同一画面にエラーメッセージが表示され、ホーム画面へ遷移しない。</t>
+    <t>同一画面にエラーメッセージ（MSG003）が表示され、ホーム画面へ遷移しない。</t>
   </si>
   <si>
     <t>異常系</t>
@@ -166,7 +169,7 @@
     <t>ユーザーIDを空欄、パスワードのみ入力する。</t>
   </si>
   <si>
-    <t>同一画面にエラーメッセージが表示され、ログインできない。</t>
+    <t>同一画面にエラーメッセージ（MSG001）が表示され、ログインできない。</t>
   </si>
   <si>
     <t>必須チェック</t>
@@ -181,6 +184,9 @@
     <t>パスワードを空欄、ユーザーIDのみ入力する。</t>
   </si>
   <si>
+    <t>同一画面にエラーメッセージ（MSG002）が表示され、ログインできない。</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -235,7 +241,7 @@
     <t>未出勤状態でホーム画面を表示する。</t>
   </si>
   <si>
-    <t>出勤時刻が登録され、結果メッセージが表示され、当日の勤怠状態が勤務中に更新される。</t>
+    <t>出勤時刻が登録され、MSG004 が表示され、当日の勤怠状態が勤務中に更新される。</t>
   </si>
   <si>
     <t>10</t>
@@ -247,7 +253,7 @@
     <t>当日すでに出勤打刻済みである。</t>
   </si>
   <si>
-    <t>出勤ボタンが非活性、または押下時に「既に出勤済みです。」等のメッセージが表示される。</t>
+    <t>出勤ボタンが非活性、または押下時に MSG005 が表示される。</t>
   </si>
   <si>
     <t>11</t>
@@ -268,7 +274,7 @@
     <t>退勤ボタン押下で退勤打刻できることを確認する。</t>
   </si>
   <si>
-    <t>退勤時刻が登録され、結果メッセージが表示され、当日の勤怠状態が退勤済みに更新される。</t>
+    <t>退勤時刻が登録され、MSG006 が表示され、当日の勤怠状態が退勤済みに更新される。</t>
   </si>
   <si>
     <t>13</t>
@@ -280,7 +286,7 @@
     <t>当日の出勤打刻が未登録である。</t>
   </si>
   <si>
-    <t>退勤ボタンが非活性、または押下時に「出勤前のため退勤できません。」等のメッセージが表示される。</t>
+    <t>退勤ボタンが非活性、または押下時に MSG007 が表示される。</t>
   </si>
   <si>
     <t>14</t>
@@ -304,7 +310,7 @@
     <t>当日休憩開始打刻済みである。</t>
   </si>
   <si>
-    <t>休憩終了ボタンが押下可能になり、休憩開始ボタンは押下不可となる。</t>
+    <t>休憩開始時刻が登録され、MSG008 が表示され、当日の勤怠状態が休憩中に更新される。</t>
   </si>
   <si>
     <t>16</t>
@@ -325,7 +331,7 @@
     <t>休憩開始打刻が未登録である。</t>
   </si>
   <si>
-    <t>休憩終了ボタンが非活性、または押下時に「休憩開始後に休憩終了してください。」等のメッセージが表示される。</t>
+    <t>休憩終了時刻が登録され、MSG010 が表示され、当日の勤怠状態が勤務中へ戻る。</t>
   </si>
   <si>
     <t>18</t>
@@ -337,7 +343,7 @@
     <t>ホーム画面を表示している。</t>
   </si>
   <si>
-    <t>SCR003 勤怠一覧画面へ遷移する。</t>
+    <t>休憩終了ボタンが非活性、または押下時に MSG011 が表示される。</t>
   </si>
   <si>
     <t>画面遷移</t>
@@ -466,7 +472,7 @@
     <t>対象月に勤怠データが登録されている。</t>
   </si>
   <si>
-    <t>日付は yyyy/MM/dd、時刻は HH:mm 形式で表示される。</t>
+    <t>MSG015 が表示される。</t>
   </si>
   <si>
     <t>28</t>
@@ -566,10 +572,6 @@
   </si>
   <si>
     <t>JUnit（月次抽出）</t>
-  </si>
-  <si>
-    <t>1.0</t>
-    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
@@ -713,6 +715,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -725,9 +730,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,6 +746,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -933,7 +939,7 @@
     <row r="1" spans="2:8" ht="49.95" customHeight="1"/>
     <row r="2" spans="2:8" ht="49.95" customHeight="1"/>
     <row r="3" spans="2:8" ht="49.95" customHeight="1"/>
-    <row r="4" spans="2:8" ht="30" customHeight="1">
+    <row r="4" spans="2:8">
       <c r="B4" s="7" t="s">
         <v>0</v>
       </c>
@@ -944,7 +950,7 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="2:8" ht="30" customHeight="1">
+    <row r="5" spans="2:8">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -953,7 +959,7 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="2:8" ht="30" customHeight="1">
+    <row r="6" spans="2:8">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -962,7 +968,7 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
     </row>
-    <row r="10" spans="2:8" ht="25.05" customHeight="1">
+    <row r="10" spans="2:8">
       <c r="C10" s="4" t="s">
         <v>1</v>
       </c>
@@ -973,7 +979,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
-    <row r="12" spans="2:8" ht="25.05" customHeight="1">
+    <row r="12" spans="2:8">
       <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
@@ -984,7 +990,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
-    <row r="14" spans="2:8" ht="25.05" customHeight="1">
+    <row r="14" spans="2:8">
       <c r="C14" s="4" t="s">
         <v>5</v>
       </c>
@@ -995,7 +1001,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
-    <row r="16" spans="2:8" ht="25.05" customHeight="1">
+    <row r="16" spans="2:8">
       <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
@@ -1006,7 +1012,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="18" spans="3:7" ht="25.05" customHeight="1">
+    <row r="18" spans="3:7">
       <c r="C18" s="4" t="s">
         <v>9</v>
       </c>
@@ -1017,13 +1023,13 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="20" spans="3:7" ht="25.05" customHeight="1">
+    <row r="20" spans="3:7">
       <c r="C20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="5"/>
-      <c r="E20" s="13" t="s">
-        <v>180</v>
+      <c r="E20" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -1060,19 +1066,19 @@
   <dimension ref="A1:J43"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.95" customHeight="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:10" ht="26.4">
+      <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="5"/>
@@ -1085,9 +1091,9 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1">
-      <c r="A2" s="12" t="s">
-        <v>12</v>
+    <row r="2" spans="1:10" ht="15">
+      <c r="A2" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1099,976 +1105,976 @@
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" spans="1:10" ht="24" customHeight="1">
-      <c r="A5" s="9" t="s">
+    <row r="4" spans="1:10" ht="18">
+      <c r="A4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-    </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:10" ht="24" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:10" ht="18">
+      <c r="A6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="9" spans="1:10" ht="28.05" customHeight="1">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="9" spans="1:10" ht="16.2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="36" customHeight="1">
+    <row r="10" spans="1:10" ht="32.4">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="36" customHeight="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16.2">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="36" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="32.4">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="36" customHeight="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="32.4">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="36" customHeight="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="32.4">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="36" customHeight="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="32.4">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="36" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="32.4">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="36" customHeight="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="32.4">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="36" customHeight="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="32.4">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="36" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16.2">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="36" customHeight="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16.2">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="36" customHeight="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="32.4">
       <c r="A21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="36" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16.2">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="36" customHeight="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="32.4">
       <c r="A23" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="36" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="32.4">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="36" customHeight="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="32.4">
       <c r="A25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="36" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="32.4">
       <c r="A26" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="36" customHeight="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16.2">
       <c r="A27" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="36" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="32.4">
       <c r="A28" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="36" customHeight="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="32.4">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="36" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="32.4">
       <c r="A30" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="36" customHeight="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="16.2">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="36" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="16.2">
       <c r="A32" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="36" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="16.2">
       <c r="A33" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="36" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="32.4">
       <c r="A34" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="36" customHeight="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="32.4">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="36" customHeight="1">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="16.2">
       <c r="A36" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="36" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="32.4">
       <c r="A37" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="36" customHeight="1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="16.2">
       <c r="A38" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="48" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="32.4">
       <c r="A39" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="48" customHeight="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="32.4">
       <c r="A40" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="48" customHeight="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="32.4">
       <c r="A41" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="48" customHeight="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="32.4">
       <c r="A42" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="48" customHeight="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="32.4">
       <c r="A43" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2082,6 +2088,6 @@
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="33" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>